--- a/Packages/cn.etetet.twsunit/Luban/Config/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.twsunit/Luban/Config/Datas/Unit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -111,6 +111,24 @@
   </si>
   <si>
     <t>Role_2</t>
+  </si>
+  <si>
+    <t>普通怪</t>
+  </si>
+  <si>
+    <t>小萝卜</t>
+  </si>
+  <si>
+    <t>Monster_1</t>
+  </si>
+  <si>
+    <t>精英怪</t>
+  </si>
+  <si>
+    <t>大罗卜</t>
+  </si>
+  <si>
+    <t>Monster_2</t>
   </si>
 </sst>
 </file>
@@ -737,17 +755,25 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="22" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1071,14 +1097,14 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
-    <col min="2" max="3" width="15.875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.75" style="2" customWidth="1"/>
+    <col min="2" max="3" width="15.875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20.75" style="3" customWidth="1"/>
     <col min="5" max="5" width="22.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="16.875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="11.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="13.25" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="13.125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="14.375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="11.25" style="3" customWidth="1"/>
+    <col min="10" max="10" width="14.75" style="3" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1086,31 +1112,31 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1118,31 +1144,31 @@
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1150,97 +1176,149 @@
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="2:10">
-      <c r="B4" s="3">
+      <c r="B4" s="5">
         <v>1001</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="5">
         <v>20</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="5">
         <v>100</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="5">
         <v>1</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="3">
         <v>1</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="2:10">
-      <c r="B5" s="3">
+      <c r="B5" s="5">
         <v>1002</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="5">
         <v>30</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="5">
         <v>200</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="5">
         <v>2</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="3">
         <v>2</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="3" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10">
+      <c r="B6" s="3">
+        <v>1101</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="3">
+        <v>10</v>
+      </c>
+      <c r="G6" s="3">
+        <v>20</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="B7" s="3">
+        <v>1102</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="3">
+        <v>20</v>
+      </c>
+      <c r="G7" s="3">
+        <v>40</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="6:6">
-      <c r="F8" s="5"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9" spans="6:6">
-      <c r="F9" s="5"/>
+      <c r="F9" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Packages/cn.etetet.twsunit/Luban/Config/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.twsunit/Luban/Config/Datas/Unit.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -44,16 +44,7 @@
     <t>Des</t>
   </si>
   <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>Hp</t>
-  </si>
-  <si>
-    <t>CriticalHit</t>
-  </si>
-  <si>
-    <t>SkillHit</t>
+    <t>*NumericTypeValue</t>
   </si>
   <si>
     <t>ResName</t>
@@ -68,6 +59,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>map,ENumericType,long</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -80,16 +74,7 @@
     <t>描述</t>
   </si>
   <si>
-    <t>基础攻击</t>
-  </si>
-  <si>
-    <t>基础生命</t>
-  </si>
-  <si>
-    <t>暴击伤害</t>
-  </si>
-  <si>
-    <t>技能伤害</t>
+    <t>数值</t>
   </si>
   <si>
     <t>图片名称</t>
@@ -104,7 +89,37 @@
     <t>带有强力攻击技能</t>
   </si>
   <si>
+    <t>普攻伤害_0</t>
+  </si>
+  <si>
     <t>Role_1</t>
+  </si>
+  <si>
+    <t>当前血量_0</t>
+  </si>
+  <si>
+    <t>最大血量_1</t>
+  </si>
+  <si>
+    <t>暴击伤害_1</t>
+  </si>
+  <si>
+    <t>技能伤害_1</t>
+  </si>
+  <si>
+    <t>速度_1</t>
+  </si>
+  <si>
+    <t>等级_0</t>
+  </si>
+  <si>
+    <t>经验值_0</t>
+  </si>
+  <si>
+    <t>金钱_0</t>
+  </si>
+  <si>
+    <t>钻石_0</t>
   </si>
   <si>
     <t>米克尔1</t>
@@ -771,8 +786,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1093,22 +1108,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21"/>
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
     <col min="2" max="3" width="15.875" style="3" customWidth="1"/>
     <col min="4" max="4" width="20.75" style="3" customWidth="1"/>
     <col min="5" max="5" width="22.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="16.875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="13.125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="14.375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="11.25" style="3" customWidth="1"/>
-    <col min="10" max="10" width="14.75" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="6" max="7" width="31.125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="14.75" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1127,200 +1139,512 @@
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="4"/>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:8">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="B2" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:8">
+      <c r="A3" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="2:10">
+    </row>
+    <row r="4" s="2" customFormat="1" spans="2:8">
       <c r="B4" s="5">
         <v>1001</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="7">
+        <v>20</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" spans="2:8">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="G5" s="7">
+        <v>100</v>
+      </c>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="2:8">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="G6" s="7">
+        <v>100</v>
+      </c>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="2:8">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="5">
+      <c r="G7" s="7">
+        <v>10000</v>
+      </c>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="2:8">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="7">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" s="2" customFormat="1" spans="2:8">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="7">
+        <v>10000</v>
+      </c>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" s="2" customFormat="1" spans="2:8">
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="7">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" s="2" customFormat="1" spans="2:8">
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="2:8">
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="7">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" s="2" customFormat="1" spans="2:8">
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="7">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="2:8">
+      <c r="B14" s="5">
+        <v>1002</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="5">
-        <v>100</v>
-      </c>
-      <c r="H4" s="5">
+      <c r="G14" s="7">
+        <v>30</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="2:8">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="7">
+        <v>200</v>
+      </c>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="2:8">
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="7">
+        <v>200</v>
+      </c>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="2:8">
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="7">
+        <v>20000</v>
+      </c>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="2:8">
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="7">
+        <v>20000</v>
+      </c>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="2:8">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="7">
+        <v>20000</v>
+      </c>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="2:8">
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="7">
         <v>1</v>
       </c>
-      <c r="I4" s="3">
-        <v>1</v>
-      </c>
-      <c r="J4" s="3" t="s">
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="2:8">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="7">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" s="2" customFormat="1" spans="2:8">
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" s="7">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" s="2" customFormat="1" spans="2:8">
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G23" s="7">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" s="2" customFormat="1" spans="2:8">
+      <c r="B24" s="3">
+        <v>1101</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="3">
+        <v>10</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" spans="2:8">
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="7">
+        <v>20</v>
+      </c>
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" s="2" customFormat="1" spans="2:8">
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="7">
+        <v>20</v>
+      </c>
+      <c r="H26" s="3"/>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="2:8">
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27" s="7">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28" s="2" customFormat="1" spans="2:8">
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="2:10">
-      <c r="B5" s="5">
-        <v>1002</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="G28" s="7">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3"/>
+    </row>
+    <row r="29" s="2" customFormat="1" spans="2:8">
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="7">
+        <v>10000</v>
+      </c>
+      <c r="H29" s="3"/>
+    </row>
+    <row r="30" s="2" customFormat="1" spans="2:8">
+      <c r="B30" s="3">
+        <v>1102</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="3">
+        <v>20</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" spans="2:8">
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="G31" s="7">
+        <v>40</v>
+      </c>
+      <c r="H31" s="3"/>
+    </row>
+    <row r="32" s="2" customFormat="1" spans="2:8">
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="7">
+        <v>40</v>
+      </c>
+      <c r="H32" s="3"/>
+    </row>
+    <row r="33" s="2" customFormat="1" spans="2:8">
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G33" s="7">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3"/>
+    </row>
+    <row r="34" s="2" customFormat="1" spans="2:8">
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G34" s="7">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3"/>
+    </row>
+    <row r="35" spans="6:7">
+      <c r="F35" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="5">
-        <v>30</v>
-      </c>
-      <c r="G5" s="5">
-        <v>200</v>
-      </c>
-      <c r="H5" s="5">
-        <v>2</v>
-      </c>
-      <c r="I5" s="3">
-        <v>2</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10">
-      <c r="B6" s="3">
-        <v>1101</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="3">
-        <v>10</v>
-      </c>
-      <c r="G6" s="3">
-        <v>20</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10">
-      <c r="B7" s="3">
-        <v>1102</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="3">
-        <v>20</v>
-      </c>
-      <c r="G7" s="3">
-        <v>40</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="6:6">
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="6:6">
-      <c r="F9" s="7"/>
+      <c r="G35" s="3">
+        <v>20000</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/Packages/cn.etetet.twsunit/Luban/Config/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.twsunit/Luban/Config/Datas/Unit.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -144,6 +144,12 @@
   </si>
   <si>
     <t>Monster_2</t>
+  </si>
+  <si>
+    <t>特效</t>
+  </si>
+  <si>
+    <t>普通攻击</t>
   </si>
 </sst>
 </file>
@@ -1108,7 +1114,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
@@ -1639,6 +1645,17 @@
         <v>20000</v>
       </c>
     </row>
+    <row r="36" spans="2:4">
+      <c r="B36" s="3">
+        <v>2001</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="F1:G1"/>

--- a/Packages/cn.etetet.twsunit/Luban/Config/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.twsunit/Luban/Config/Datas/Unit.xlsx
@@ -4,10 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="21600" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
+    <sheet name="MonsterPoto" sheetId="2" r:id="rId2"/>
+    <sheet name="WeaponProto" sheetId="3" r:id="rId3"/>
+    <sheet name="ParticleProto" sheetId="4" r:id="rId4"/>
+    <sheet name="NoneProto" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="75">
   <si>
     <t>##var</t>
   </si>
@@ -47,6 +51,9 @@
     <t>*NumericTypeValue</t>
   </si>
   <si>
+    <t>*InitCastDatas</t>
+  </si>
+  <si>
     <t>ResName</t>
   </si>
   <si>
@@ -62,6 +69,9 @@
     <t>map,ENumericType,long</t>
   </si>
   <si>
+    <t>list,InitCastData</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -77,7 +87,10 @@
     <t>数值</t>
   </si>
   <si>
-    <t>图片名称</t>
+    <t>初始化技能数据</t>
+  </si>
+  <si>
+    <t>资源名称</t>
   </si>
   <si>
     <t>玩家</t>
@@ -89,12 +102,27 @@
     <t>带有强力攻击技能</t>
   </si>
   <si>
-    <t>普攻伤害_0</t>
+    <t>对局等级_0</t>
+  </si>
+  <si>
+    <t>0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,1</t>
   </si>
   <si>
     <t>Role_1</t>
   </si>
   <si>
+    <t>对局经验值_0</t>
+  </si>
+  <si>
+    <t>对局金币_0</t>
+  </si>
+  <si>
+    <t>普攻伤害_1</t>
+  </si>
+  <si>
     <t>当前血量_0</t>
   </si>
   <si>
@@ -104,22 +132,28 @@
     <t>暴击伤害_1</t>
   </si>
   <si>
-    <t>技能伤害_1</t>
+    <t>攻击范围_1</t>
+  </si>
+  <si>
+    <t>吸收范围_1</t>
+  </si>
+  <si>
+    <t>对局金币倍率_0</t>
+  </si>
+  <si>
+    <t>对局经验值倍率_0</t>
   </si>
   <si>
     <t>速度_1</t>
   </si>
   <si>
-    <t>等级_0</t>
-  </si>
-  <si>
-    <t>经验值_0</t>
-  </si>
-  <si>
-    <t>金钱_0</t>
-  </si>
-  <si>
-    <t>钻石_0</t>
+    <t>防御_1</t>
+  </si>
+  <si>
+    <t>攻击间隔_1</t>
+  </si>
+  <si>
+    <t>暴击率_1</t>
   </si>
   <si>
     <t>米克尔1</t>
@@ -128,28 +162,100 @@
     <t>Role_2</t>
   </si>
   <si>
-    <t>普通怪</t>
-  </si>
-  <si>
-    <t>小萝卜</t>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>Stone</t>
   </si>
   <si>
     <t>Monster_1</t>
   </si>
   <si>
-    <t>精英怪</t>
-  </si>
-  <si>
-    <t>大罗卜</t>
+    <t>精英</t>
+  </si>
+  <si>
+    <t>Skeleton</t>
   </si>
   <si>
     <t>Monster_2</t>
   </si>
   <si>
+    <t>统领</t>
+  </si>
+  <si>
+    <t>Bat</t>
+  </si>
+  <si>
+    <t>Monster_3</t>
+  </si>
+  <si>
+    <t>首领</t>
+  </si>
+  <si>
+    <t>Tree</t>
+  </si>
+  <si>
+    <t>Monster_4</t>
+  </si>
+  <si>
+    <t>武器</t>
+  </si>
+  <si>
+    <t>枪</t>
+  </si>
+  <si>
+    <t>0,0.5,0</t>
+  </si>
+  <si>
+    <t>qiang</t>
+  </si>
+  <si>
+    <t>法杖</t>
+  </si>
+  <si>
+    <t>quanzhang</t>
+  </si>
+  <si>
     <t>特效</t>
   </si>
   <si>
-    <t>普通攻击</t>
+    <t>普攻命中特效</t>
+  </si>
+  <si>
+    <t>禁止跟随_0</t>
+  </si>
+  <si>
+    <t>AttackHit</t>
+  </si>
+  <si>
+    <t>火箭爆炸</t>
+  </si>
+  <si>
+    <t>Boom</t>
+  </si>
+  <si>
+    <t>燃烧瓶爆炸</t>
+  </si>
+  <si>
+    <t>灼烧</t>
+  </si>
+  <si>
+    <t>Burn</t>
+  </si>
+  <si>
+    <t>子弹</t>
+  </si>
+  <si>
+    <t>碰撞后消失</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>技能</t>
+  </si>
+  <si>
+    <t>碰撞后不消失</t>
   </si>
 </sst>
 </file>
@@ -162,7 +268,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,6 +279,20 @@
     <font>
       <b/>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -322,7 +442,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -332,6 +452,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -646,144 +772,154 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -792,7 +928,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1114,556 +1262,1502 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" outlineLevelCol="7"/>
+  <dimension ref="A1:K34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
+    <col min="1" max="1" width="12.5" style="3" customWidth="1"/>
     <col min="2" max="3" width="15.875" style="3" customWidth="1"/>
     <col min="4" max="4" width="20.75" style="3" customWidth="1"/>
-    <col min="5" max="5" width="22.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="22.375" style="3" customWidth="1"/>
     <col min="6" max="7" width="31.125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="14.75" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="8" max="11" width="25.125" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:8">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:8">
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:8">
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="2:8">
-      <c r="B4" s="5">
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" s="3" customFormat="1" spans="2:11">
+      <c r="B4" s="9">
         <v>1001</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="7" t="s">
+      <c r="C4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="7">
+      <c r="D4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" s="3" customFormat="1" spans="2:7">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" spans="2:7">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="3" customFormat="1" spans="2:7">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="4">
         <v>20</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="2:8">
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="7" t="s">
+    </row>
+    <row r="8" s="3" customFormat="1" spans="2:7">
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" s="3" customFormat="1" spans="2:7">
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" s="3" customFormat="1" spans="2:7">
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" s="3" customFormat="1" spans="2:7">
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" s="3" customFormat="1" spans="2:7">
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" s="3" customFormat="1" spans="2:7">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" s="3" customFormat="1" spans="2:7">
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" s="3" customFormat="1" spans="2:7">
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="16" s="3" customFormat="1" spans="2:7">
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" s="3" customFormat="1" spans="2:7">
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" s="3" customFormat="1" spans="2:7">
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" s="8" customFormat="1" spans="1:7">
+      <c r="A19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+    </row>
+    <row r="20" s="3" customFormat="1" spans="2:11">
+      <c r="B20" s="9">
+        <v>1002</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="7">
+      <c r="F20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="4">
+        <v>1</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" s="3" customFormat="1" spans="2:7">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" s="3" customFormat="1" spans="2:7">
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" s="3" customFormat="1" spans="2:7">
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" s="3" customFormat="1" spans="2:7">
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24" s="4">
         <v>100</v>
       </c>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="2:8">
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="7">
+    </row>
+    <row r="25" s="3" customFormat="1" spans="2:7">
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25" s="4">
         <v>100</v>
       </c>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="2:8">
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="7">
-        <v>10000</v>
-      </c>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="2:8">
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="7">
-        <v>10000</v>
-      </c>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="2:8">
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="7">
-        <v>10000</v>
-      </c>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="2:8">
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="7">
-        <v>1</v>
-      </c>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="2:8">
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="7">
+    </row>
+    <row r="26" s="3" customFormat="1" spans="2:7">
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" s="3" customFormat="1" spans="2:7">
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" s="3" customFormat="1" spans="2:7">
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G28" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="6:7">
+      <c r="F29" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G29" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="6:7">
+      <c r="F30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="6:7">
+      <c r="F31" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G31" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="32" spans="6:7">
+      <c r="F32" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G32" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="6:7">
+      <c r="F33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G33" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="6:7">
+      <c r="F34" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G34" s="4">
         <v>0</v>
       </c>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="2:8">
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="7">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="2:8">
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="7">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="2:8">
-      <c r="B14" s="5">
-        <v>1002</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="7">
-        <v>30</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="2:8">
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="7">
-        <v>200</v>
-      </c>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="2:8">
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="7">
-        <v>200</v>
-      </c>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="2:8">
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="7">
-        <v>20000</v>
-      </c>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="2:8">
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" s="7">
-        <v>20000</v>
-      </c>
-      <c r="H18" s="3"/>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="2:8">
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="7">
-        <v>20000</v>
-      </c>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="2:8">
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G20" s="7">
-        <v>1</v>
-      </c>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="2:8">
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G21" s="7">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" s="2" customFormat="1" spans="2:8">
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G22" s="7">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" s="2" customFormat="1" spans="2:8">
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G23" s="7">
-        <v>0</v>
-      </c>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" s="2" customFormat="1" spans="2:8">
-      <c r="B24" s="3">
-        <v>1101</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G24" s="3">
-        <v>10</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="2:8">
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G25" s="7">
-        <v>20</v>
-      </c>
-      <c r="H25" s="3"/>
-    </row>
-    <row r="26" s="2" customFormat="1" spans="2:8">
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" s="7">
-        <v>20</v>
-      </c>
-      <c r="H26" s="3"/>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="2:8">
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G27" s="7">
-        <v>0</v>
-      </c>
-      <c r="H27" s="3"/>
-    </row>
-    <row r="28" s="2" customFormat="1" spans="2:8">
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G28" s="7">
-        <v>0</v>
-      </c>
-      <c r="H28" s="3"/>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="2:8">
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="7">
-        <v>10000</v>
-      </c>
-      <c r="H29" s="3"/>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="2:8">
-      <c r="B30" s="3">
-        <v>1102</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E30" s="2"/>
-      <c r="F30" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="3">
-        <v>20</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="2:8">
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G31" s="7">
-        <v>40</v>
-      </c>
-      <c r="H31" s="3"/>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="2:8">
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G32" s="7">
-        <v>40</v>
-      </c>
-      <c r="H32" s="3"/>
-    </row>
-    <row r="33" s="2" customFormat="1" spans="2:8">
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G33" s="7">
-        <v>0</v>
-      </c>
-      <c r="H33" s="3"/>
-    </row>
-    <row r="34" s="2" customFormat="1" spans="2:8">
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G34" s="7">
-        <v>0</v>
-      </c>
-      <c r="H34" s="3"/>
-    </row>
-    <row r="35" spans="6:7">
-      <c r="F35" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="3">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4">
-      <c r="B36" s="3">
-        <v>2001</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>40</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:J1"/>
     <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:J2"/>
     <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K30"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21"/>
+  <cols>
+    <col min="1" max="1" width="12.5" style="3" customWidth="1"/>
+    <col min="2" max="3" width="15.875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20.75" style="3" customWidth="1"/>
+    <col min="5" max="5" width="22.375" style="3" customWidth="1"/>
+    <col min="6" max="7" width="31.125" style="3" customWidth="1"/>
+    <col min="8" max="11" width="25.125" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" s="3" customFormat="1" spans="2:11">
+      <c r="B4" s="3">
+        <v>2001</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="3">
+        <v>10</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" s="3" customFormat="1" spans="2:7">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" spans="2:7">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" s="3" customFormat="1" spans="2:7">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" s="3" customFormat="1" spans="2:7">
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="4">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="9" s="3" customFormat="1" spans="2:7">
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" s="8" customFormat="1" spans="1:6">
+      <c r="A10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+    </row>
+    <row r="11" s="3" customFormat="1" spans="2:11">
+      <c r="B11" s="3">
+        <v>2002</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="3">
+        <v>10</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" s="3" customFormat="1" spans="2:7">
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" s="3" customFormat="1" spans="2:7">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" s="12" customFormat="1" spans="6:7">
+      <c r="F14" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" s="12" customFormat="1" spans="6:7">
+      <c r="F15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="4">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="16" s="12" customFormat="1" spans="6:7">
+      <c r="F16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" s="8" customFormat="1" spans="1:6">
+      <c r="A17" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="F17" s="14"/>
+    </row>
+    <row r="18" s="3" customFormat="1" spans="2:11">
+      <c r="B18" s="3">
+        <v>2003</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="3">
+        <v>10</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" s="3" customFormat="1" spans="2:7">
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" s="3" customFormat="1" spans="2:7">
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" s="12" customFormat="1" spans="6:7">
+      <c r="F21" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" s="12" customFormat="1" spans="6:7">
+      <c r="F22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="4">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="23" s="12" customFormat="1" spans="6:7">
+      <c r="F23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" s="8" customFormat="1" spans="1:6">
+      <c r="A24" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="F24" s="14"/>
+    </row>
+    <row r="25" s="3" customFormat="1" spans="2:11">
+      <c r="B25" s="3">
+        <v>2004</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G25" s="3">
+        <v>10</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" s="3" customFormat="1" spans="2:7">
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G26" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" s="3" customFormat="1" spans="2:7">
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" s="3" customFormat="1" spans="6:7">
+      <c r="F28" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="6:7">
+      <c r="F29" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G29" s="4">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="30" spans="6:7">
+      <c r="F30" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21"/>
+  <cols>
+    <col min="1" max="1" width="12.5" style="7" customWidth="1"/>
+    <col min="2" max="3" width="15.875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20.75" style="3" customWidth="1"/>
+    <col min="5" max="5" width="22.375" style="7" customWidth="1"/>
+    <col min="6" max="7" width="31.125" style="3" customWidth="1"/>
+    <col min="8" max="11" width="25.125" style="7" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="5" customFormat="1" spans="1:11">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" s="5" customFormat="1" spans="1:11">
+      <c r="A2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" s="5" customFormat="1" spans="1:11">
+      <c r="A3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" spans="2:11">
+      <c r="B4" s="3">
+        <v>3001</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" s="6" customFormat="1" spans="1:11">
+      <c r="A5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="K5" s="8"/>
+    </row>
+    <row r="6" ht="22.5" spans="2:11">
+      <c r="B6" s="3">
+        <v>3002</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="3">
+        <v>2</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="8:11">
+      <c r="H7" s="3"/>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" customFormat="1" spans="1:11">
+      <c r="A8" s="7"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" customFormat="1" spans="1:11">
+      <c r="A9" s="7"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="K9" s="3"/>
+    </row>
+    <row r="10" s="7" customFormat="1" ht="22.5" spans="2:11">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11" spans="8:11">
+      <c r="H11" s="3"/>
+      <c r="K11" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21"/>
+  <cols>
+    <col min="1" max="1" width="12.5" style="3" customWidth="1"/>
+    <col min="2" max="3" width="15.875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20.75" style="3" customWidth="1"/>
+    <col min="5" max="5" width="22.375" style="3" customWidth="1"/>
+    <col min="6" max="7" width="31.125" style="3" customWidth="1"/>
+    <col min="8" max="11" width="25.125" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" s="3" customFormat="1" spans="2:11">
+      <c r="B4" s="3">
+        <v>4001</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" s="3" customFormat="1" spans="2:11">
+      <c r="B5" s="3">
+        <v>4002</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11">
+      <c r="B6" s="3">
+        <v>4003</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11">
+      <c r="B7" s="3">
+        <v>4004</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="6:6">
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="6:6">
+      <c r="F9" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="4"/>
+  <cols>
+    <col min="1" max="1" width="10" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="23.5" style="2" customWidth="1"/>
+    <col min="8" max="9" width="9" style="2"/>
+    <col min="10" max="10" width="16.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="13.25" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="21" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="21" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="21" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11">
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Packages/cn.etetet.twsunit/Luban/Config/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.twsunit/Luban/Config/Datas/Unit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" activeTab="4"/>
+    <workbookView windowHeight="17655" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="74">
   <si>
     <t>##var</t>
   </si>
@@ -243,19 +243,16 @@
     <t>Burn</t>
   </si>
   <si>
-    <t>子弹</t>
-  </si>
-  <si>
-    <t>碰撞后消失</t>
+    <t>技能</t>
   </si>
   <si>
     <t>None</t>
   </si>
   <si>
-    <t>技能</t>
-  </si>
-  <si>
-    <t>碰撞后不消失</t>
+    <t>能量块</t>
+  </si>
+  <si>
+    <t>摄像机</t>
   </si>
 </sst>
 </file>
@@ -1477,7 +1474,7 @@
         <v>34</v>
       </c>
       <c r="G12" s="4">
-        <v>10</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" spans="2:7">
@@ -1513,7 +1510,7 @@
         <v>37</v>
       </c>
       <c r="G15" s="4">
-        <v>100000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" spans="2:7">
@@ -1688,7 +1685,7 @@
         <v>34</v>
       </c>
       <c r="G28" s="4">
-        <v>10</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="29" spans="6:7">
@@ -2620,8 +2617,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="4"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.125" style="2" customWidth="1"/>
@@ -2724,11 +2721,8 @@
       <c r="D4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="5" spans="2:11">
@@ -2736,16 +2730,27 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11">
+      <c r="B6" s="2">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>72</v>
+      <c r="K6" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.twsunit/Luban/Config/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.twsunit/Luban/Config/Datas/Unit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="4"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="76">
   <si>
     <t>##var</t>
   </si>
@@ -51,7 +51,10 @@
     <t>*NumericTypeValue</t>
   </si>
   <si>
-    <t>*InitCastDatas</t>
+    <t>*InitCastConfigIds</t>
+  </si>
+  <si>
+    <t>InitScale</t>
   </si>
   <si>
     <t>ResName</t>
@@ -69,7 +72,10 @@
     <t>map,ENumericType,long</t>
   </si>
   <si>
-    <t>list,InitCastData</t>
+    <t>list,int</t>
+  </si>
+  <si>
+    <t>(list#sep=,),float</t>
   </si>
   <si>
     <t>##</t>
@@ -90,6 +96,9 @@
     <t>初始化技能数据</t>
   </si>
   <si>
+    <t>初始缩放</t>
+  </si>
+  <si>
     <t>资源名称</t>
   </si>
   <si>
@@ -105,10 +114,7 @@
     <t>对局等级_0</t>
   </si>
   <si>
-    <t>0,0,0</t>
-  </si>
-  <si>
-    <t>1,1,1</t>
+    <t>0.3,0.3</t>
   </si>
   <si>
     <t>Role_1</t>
@@ -168,6 +174,9 @@
     <t>Stone</t>
   </si>
   <si>
+    <t>0.4,0.4</t>
+  </si>
+  <si>
     <t>Monster_1</t>
   </si>
   <si>
@@ -202,9 +211,6 @@
   </si>
   <si>
     <t>枪</t>
-  </si>
-  <si>
-    <t>0,0.5,0</t>
   </si>
   <si>
     <t>qiang</t>
@@ -899,7 +905,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -907,6 +913,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1259,19 +1266,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="3" customWidth="1"/>
-    <col min="2" max="3" width="15.875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.75" style="3" customWidth="1"/>
-    <col min="5" max="5" width="22.375" style="3" customWidth="1"/>
-    <col min="6" max="7" width="31.125" style="3" customWidth="1"/>
-    <col min="8" max="11" width="25.125" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="12.5" style="4" customWidth="1"/>
+    <col min="2" max="3" width="15.875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="20.75" style="4" customWidth="1"/>
+    <col min="5" max="5" width="22.375" style="4" customWidth="1"/>
+    <col min="6" max="7" width="31.125" style="4" customWidth="1"/>
+    <col min="8" max="10" width="25.125" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
+    <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1290,460 +1297,460 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" s="4" customFormat="1" spans="2:10">
+      <c r="B4" s="10">
+        <v>1001</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" s="4" customFormat="1" spans="2:7">
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" s="4" customFormat="1" spans="2:7">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="4" customFormat="1" spans="2:7">
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" s="4" customFormat="1" spans="2:7">
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" s="4" customFormat="1" spans="2:7">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" s="4" customFormat="1" spans="2:7">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" s="4" customFormat="1" spans="2:7">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" s="4" customFormat="1" spans="2:7">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="13" s="4" customFormat="1" spans="2:7">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" s="4" customFormat="1" spans="2:7">
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" s="4" customFormat="1" spans="2:7">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="5">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="16" s="4" customFormat="1" spans="2:7">
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="5">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+    </row>
+    <row r="17" s="4" customFormat="1" spans="2:7">
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" s="4" customFormat="1" spans="2:7">
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" s="9" customFormat="1" spans="1:7">
+      <c r="A19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+    </row>
+    <row r="20" s="4" customFormat="1" spans="2:10">
+      <c r="B20" s="10">
+        <v>1002</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="5">
+        <v>1</v>
+      </c>
+      <c r="H20" s="4">
+        <v>1</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" s="4" customFormat="1" spans="2:7">
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" s="4" customFormat="1" spans="2:7">
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" s="4" customFormat="1" spans="2:7">
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" s="4" customFormat="1" spans="2:7">
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" s="4" customFormat="1" spans="2:7">
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" s="4" customFormat="1" spans="2:7">
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G26" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" s="4" customFormat="1" spans="2:7">
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G27" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" s="4" customFormat="1" spans="2:7">
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G28" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="29" spans="6:7">
+      <c r="F29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G29" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="6:7">
+      <c r="F30" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G30" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="6:7">
+      <c r="F31" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G31" s="5">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="32" spans="6:7">
+      <c r="F32" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G32" s="5">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" s="3" customFormat="1" spans="2:11">
-      <c r="B4" s="9">
-        <v>1001</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="4">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3">
-        <v>1</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" s="3" customFormat="1" spans="2:7">
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="4">
+    </row>
+    <row r="33" spans="6:7">
+      <c r="F33" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G33" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="6:7">
+      <c r="F34" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G34" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" spans="2:7">
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="3" customFormat="1" spans="2:7">
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" s="3" customFormat="1" spans="2:7">
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" s="3" customFormat="1" spans="2:7">
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" s="3" customFormat="1" spans="2:7">
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" s="3" customFormat="1" spans="2:7">
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" s="3" customFormat="1" spans="2:7">
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="4">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="13" s="3" customFormat="1" spans="2:7">
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" s="3" customFormat="1" spans="2:7">
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" s="3" customFormat="1" spans="2:7">
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G15" s="4">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="16" s="3" customFormat="1" spans="2:7">
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" s="3" customFormat="1" spans="2:7">
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" s="3" customFormat="1" spans="2:7">
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G18" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" s="8" customFormat="1" spans="1:7">
-      <c r="A19" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-    </row>
-    <row r="20" s="3" customFormat="1" spans="2:11">
-      <c r="B20" s="9">
-        <v>1002</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="4">
-        <v>1</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" s="3" customFormat="1" spans="2:7">
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G21" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" s="3" customFormat="1" spans="2:7">
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G22" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" s="3" customFormat="1" spans="2:7">
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G23" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" s="3" customFormat="1" spans="2:7">
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G24" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" s="3" customFormat="1" spans="2:7">
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G25" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" s="3" customFormat="1" spans="2:7">
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" s="3" customFormat="1" spans="2:7">
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G27" s="4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" s="3" customFormat="1" spans="2:7">
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G28" s="4">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="29" spans="6:7">
-      <c r="F29" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G29" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="6:7">
-      <c r="F30" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G30" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="6:7">
-      <c r="F31" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G31" s="4">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="32" spans="6:7">
-      <c r="F32" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G32" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="6:7">
-      <c r="F33" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G33" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="6:7">
-      <c r="F34" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G34" s="4">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="3">
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:J1"/>
     <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:J2"/>
     <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1754,19 +1761,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="3" customWidth="1"/>
-    <col min="2" max="3" width="15.875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.75" style="3" customWidth="1"/>
-    <col min="5" max="5" width="22.375" style="3" customWidth="1"/>
-    <col min="6" max="7" width="31.125" style="3" customWidth="1"/>
-    <col min="8" max="11" width="25.125" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="12.5" style="4" customWidth="1"/>
+    <col min="2" max="3" width="15.875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="20.75" style="4" customWidth="1"/>
+    <col min="5" max="5" width="22.375" style="4" customWidth="1"/>
+    <col min="6" max="7" width="31.125" style="4" customWidth="1"/>
+    <col min="8" max="10" width="25.125" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
+    <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1785,421 +1792,407 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" s="4" customFormat="1" spans="2:10">
+      <c r="B4" s="4">
+        <v>2001</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="4">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="H4" s="4"/>
+      <c r="I4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" s="4" customFormat="1" spans="2:7">
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" s="4" customFormat="1" spans="2:7">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" s="4" customFormat="1" spans="2:7">
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="4">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="1" t="s">
+    </row>
+    <row r="8" s="4" customFormat="1" spans="2:7">
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="9" s="4" customFormat="1" spans="2:7">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" s="9" customFormat="1" spans="1:6">
+      <c r="A10" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+    </row>
+    <row r="11" s="4" customFormat="1" spans="2:10">
+      <c r="B11" s="4">
+        <v>2002</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="4">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="H11" s="4"/>
+      <c r="I11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" s="4" customFormat="1" spans="2:7">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" s="4" customFormat="1" spans="2:7">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" s="13" customFormat="1" spans="6:7">
+      <c r="F14" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" s="13" customFormat="1" spans="6:7">
+      <c r="F15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="16" s="13" customFormat="1" spans="6:7">
+      <c r="F16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" s="9" customFormat="1" spans="1:6">
+      <c r="A17" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" s="3" customFormat="1" spans="2:11">
-      <c r="B4" s="3">
-        <v>2001</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="3">
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="F17" s="15"/>
+    </row>
+    <row r="18" s="4" customFormat="1" spans="2:10">
+      <c r="B18" s="4">
+        <v>2003</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="4">
         <v>10</v>
       </c>
-      <c r="H4" s="3">
-        <v>1</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" s="3" customFormat="1" spans="2:7">
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="4">
+      <c r="H18" s="4"/>
+      <c r="I18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" s="4" customFormat="1" spans="2:7">
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" s="5">
         <v>20</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" spans="2:7">
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4" t="s">
+    <row r="20" s="4" customFormat="1" spans="2:7">
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" s="13" customFormat="1" spans="6:7">
+      <c r="F21" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" s="13" customFormat="1" spans="6:7">
+      <c r="F22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="23" s="13" customFormat="1" spans="6:7">
+      <c r="F23" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" s="9" customFormat="1" spans="1:6">
+      <c r="A24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="F24" s="15"/>
+    </row>
+    <row r="25" s="4" customFormat="1" spans="2:10">
+      <c r="B25" s="4">
+        <v>2004</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G25" s="4">
+        <v>10</v>
+      </c>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" s="4" customFormat="1" spans="2:7">
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" s="5">
         <v>20</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="1" spans="2:7">
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4" t="s">
+    <row r="27" s="4" customFormat="1" spans="2:7">
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G27" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" s="4" customFormat="1" spans="6:7">
+      <c r="F28" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G28" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="8" s="3" customFormat="1" spans="2:7">
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="4">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="9" s="3" customFormat="1" spans="2:7">
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" s="8" customFormat="1" spans="1:6">
-      <c r="A10" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-    </row>
-    <row r="11" s="3" customFormat="1" spans="2:11">
-      <c r="B11" s="3">
-        <v>2002</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="3">
-        <v>10</v>
-      </c>
-      <c r="H11" s="3">
-        <v>1</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" s="3" customFormat="1" spans="2:7">
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" s="3" customFormat="1" spans="2:7">
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" s="12" customFormat="1" spans="6:7">
-      <c r="F14" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" s="12" customFormat="1" spans="6:7">
-      <c r="F15" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G15" s="4">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="16" s="12" customFormat="1" spans="6:7">
-      <c r="F16" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" s="8" customFormat="1" spans="1:6">
-      <c r="A17" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="F17" s="14"/>
-    </row>
-    <row r="18" s="3" customFormat="1" spans="2:11">
-      <c r="B18" s="3">
-        <v>2003</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G18" s="3">
-        <v>10</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" s="3" customFormat="1" spans="2:7">
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G19" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" s="3" customFormat="1" spans="2:7">
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" s="12" customFormat="1" spans="6:7">
-      <c r="F21" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" s="12" customFormat="1" spans="6:7">
-      <c r="F22" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" s="4">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="23" s="12" customFormat="1" spans="6:7">
-      <c r="F23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" s="8" customFormat="1" spans="1:6">
-      <c r="A24" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="F24" s="14"/>
-    </row>
-    <row r="25" s="3" customFormat="1" spans="2:11">
-      <c r="B25" s="3">
-        <v>2004</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G25" s="3">
-        <v>10</v>
-      </c>
-      <c r="H25" s="3">
-        <v>1</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" s="3" customFormat="1" spans="2:7">
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G26" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" s="3" customFormat="1" spans="2:7">
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G27" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" s="3" customFormat="1" spans="6:7">
-      <c r="F28" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G28" s="3">
-        <v>10</v>
-      </c>
-    </row>
     <row r="29" spans="6:7">
-      <c r="F29" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G29" s="4">
-        <v>50000</v>
+      <c r="F29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G29" s="5">
+        <v>10000</v>
       </c>
     </row>
     <row r="30" spans="6:7">
-      <c r="F30" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G30" s="3">
+      <c r="F30" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G30" s="4">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="3">
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:J1"/>
     <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:J2"/>
     <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2209,20 +2202,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="7" customWidth="1"/>
-    <col min="2" max="3" width="15.875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.75" style="3" customWidth="1"/>
-    <col min="5" max="5" width="22.375" style="7" customWidth="1"/>
-    <col min="6" max="7" width="31.125" style="3" customWidth="1"/>
-    <col min="8" max="11" width="25.125" style="7" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="12.5" style="8" customWidth="1"/>
+    <col min="2" max="3" width="15.875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="20.75" style="4" customWidth="1"/>
+    <col min="5" max="5" width="22.375" style="8" customWidth="1"/>
+    <col min="6" max="7" width="31.125" style="4" customWidth="1"/>
+    <col min="8" max="10" width="25.125" style="8" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="6" customFormat="1" spans="1:10">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -2234,187 +2227,176 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1"/>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" s="5" customFormat="1" spans="1:11">
-      <c r="A2" s="5" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
+    </row>
+    <row r="2" s="6" customFormat="1" spans="1:10">
+      <c r="A2" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" s="5" customFormat="1" spans="1:11">
-      <c r="A3" s="5" t="s">
-        <v>13</v>
+    </row>
+    <row r="3" s="6" customFormat="1" spans="1:10">
+      <c r="A3" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" ht="22.5" spans="2:11">
-      <c r="B4" s="3">
+        <v>20</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" spans="2:10">
+      <c r="B4" s="4">
         <v>3001</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H4" s="3">
-        <v>1</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="5" s="6" customFormat="1" spans="1:11">
-      <c r="A5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="K5" s="8"/>
-    </row>
-    <row r="6" ht="22.5" spans="2:11">
-      <c r="B6" s="3">
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="12"/>
+      <c r="J4" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" s="7" customFormat="1" spans="1:10">
+      <c r="A5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="J5" s="9"/>
+    </row>
+    <row r="6" ht="22.5" spans="2:10">
+      <c r="B6" s="4">
         <v>3002</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H6" s="3">
+      <c r="C6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" s="4">
         <v>2</v>
       </c>
-      <c r="I6" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="8:11">
-      <c r="H7" s="3"/>
-      <c r="K7" s="3"/>
-    </row>
-    <row r="8" customFormat="1" spans="1:11">
-      <c r="A8" s="7"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" customFormat="1" spans="1:11">
-      <c r="A9" s="7"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" s="7" customFormat="1" ht="22.5" spans="2:11">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="8:11">
-      <c r="H11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="8:10">
+      <c r="H7" s="4"/>
+      <c r="J7" s="4"/>
+    </row>
+    <row r="8" customFormat="1" spans="1:10">
+      <c r="A8" s="8"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="J8" s="4"/>
+    </row>
+    <row r="9" customFormat="1" spans="1:10">
+      <c r="A9" s="8"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="J9" s="4"/>
+    </row>
+    <row r="10" s="8" customFormat="1" ht="22.5" spans="2:10">
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="8:10">
+      <c r="H11" s="4"/>
+      <c r="J11" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="3">
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:J1"/>
     <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:J2"/>
     <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2424,19 +2406,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="3" customWidth="1"/>
-    <col min="2" max="3" width="15.875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.75" style="3" customWidth="1"/>
-    <col min="5" max="5" width="22.375" style="3" customWidth="1"/>
-    <col min="6" max="7" width="31.125" style="3" customWidth="1"/>
-    <col min="8" max="11" width="25.125" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="12.5" style="4" customWidth="1"/>
+    <col min="2" max="3" width="15.875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="20.75" style="4" customWidth="1"/>
+    <col min="5" max="5" width="22.375" style="4" customWidth="1"/>
+    <col min="6" max="7" width="31.125" style="4" customWidth="1"/>
+    <col min="8" max="10" width="25.125" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
+    <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2455,159 +2437,165 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" s="3" customFormat="1" spans="2:11">
-      <c r="B4" s="3">
+      <c r="H3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" s="4" customFormat="1" spans="2:10">
+      <c r="B4" s="4">
         <v>4001</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="3">
-        <v>1</v>
-      </c>
-      <c r="K4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="5" s="3" customFormat="1" spans="2:11">
-      <c r="B5" s="3">
+      <c r="F4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" s="4" customFormat="1" spans="2:10">
+      <c r="B5" s="4">
         <v>4002</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="C5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10">
+      <c r="B6" s="4">
+        <v>4003</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="G5" s="3">
-        <v>1</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11">
-      <c r="B6" s="3">
-        <v>4003</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="D6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="B7" s="4">
+        <v>4004</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="G6" s="3">
-        <v>1</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11">
-      <c r="B7" s="3">
-        <v>4004</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7" s="3">
+      <c r="D7" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="4">
         <v>0</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>69</v>
+      <c r="J7" s="4" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="6:6">
-      <c r="F8" s="4"/>
+      <c r="F8" s="5"/>
     </row>
     <row r="9" spans="6:6">
-      <c r="F9" s="4"/>
+      <c r="F9" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="3">
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:J1"/>
     <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:J2"/>
     <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2617,7 +2605,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -2627,13 +2615,13 @@
     <col min="5" max="5" width="16.5" style="2" customWidth="1"/>
     <col min="6" max="6" width="13.375" style="2" customWidth="1"/>
     <col min="7" max="7" width="23.5" style="2" customWidth="1"/>
-    <col min="8" max="9" width="9" style="2"/>
-    <col min="10" max="10" width="16.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13.25" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="8" max="8" width="28.875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="13.25" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="21" spans="1:11">
+    <row r="1" s="1" customFormat="1" ht="21" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2652,115 +2640,121 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="21" spans="1:11">
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="21" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="21" spans="1:11">
+    </row>
+    <row r="3" s="1" customFormat="1" ht="21" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="2:11">
+      <c r="H3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10">
       <c r="B4" s="2">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11">
+        <v>72</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10">
       <c r="B5" s="2">
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11">
+        <v>74</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10">
       <c r="B6" s="2">
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>71</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="3">
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:J1"/>
     <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:J2"/>
     <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Packages/cn.etetet.twsunit/Luban/Config/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.twsunit/Luban/Config/Datas/Unit.xlsx
@@ -89,7 +89,7 @@
     <t>带有强力攻击技能</t>
   </si>
   <si>
-    <t>Role_1</t>
+    <t>Role_027</t>
   </si>
   <si>
     <t>米克尔1</t>

--- a/Packages/cn.etetet.twsunit/Luban/Config/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.twsunit/Luban/Config/Datas/Unit.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="74">
   <si>
     <t>##var</t>
   </si>
@@ -80,22 +80,175 @@
     <t>资源名称</t>
   </si>
   <si>
-    <t>玩家</t>
-  </si>
-  <si>
-    <t>米克尔</t>
-  </si>
-  <si>
-    <t>带有强力攻击技能</t>
-  </si>
-  <si>
-    <t>Role_027</t>
-  </si>
-  <si>
-    <t>米克尔1</t>
-  </si>
-  <si>
-    <t>Role_2</t>
+    <t>管理者</t>
+  </si>
+  <si>
+    <t>金钱_0</t>
+  </si>
+  <si>
+    <t>钻石_0</t>
+  </si>
+  <si>
+    <t>声望值_0</t>
+  </si>
+  <si>
+    <t>人口上限_0</t>
+  </si>
+  <si>
+    <t>农民</t>
+  </si>
+  <si>
+    <t>种植小麦、蔬菜、水果等农作物。</t>
+  </si>
+  <si>
+    <t>樵夫</t>
+  </si>
+  <si>
+    <t>砍伐数目，获取木材。</t>
+  </si>
+  <si>
+    <t>渔夫</t>
+  </si>
+  <si>
+    <t>从河流或海洋中捞捕鱼类。</t>
+  </si>
+  <si>
+    <t>矿工</t>
+  </si>
+  <si>
+    <t>开采石料、铁、铜、金、煤等矿产资源。</t>
+  </si>
+  <si>
+    <t>面包师</t>
+  </si>
+  <si>
+    <t>将小麦磨成面粉，再烤制成面包等。</t>
+  </si>
+  <si>
+    <t>厨师</t>
+  </si>
+  <si>
+    <t>将各种食材加工成高级菜肴。</t>
+  </si>
+  <si>
+    <t>铁匠</t>
+  </si>
+  <si>
+    <t>将铁锭加工成工具、武器、钉子等。</t>
+  </si>
+  <si>
+    <t>木匠</t>
+  </si>
+  <si>
+    <t>将木材加工成家具、建材、工具柄等。</t>
+  </si>
+  <si>
+    <t>裁缝</t>
+  </si>
+  <si>
+    <t>将羊毛、棉花、皮革加工成衣物、皮革制品。</t>
+  </si>
+  <si>
+    <t>陶工</t>
+  </si>
+  <si>
+    <t>制作陶器、砖块等。</t>
+  </si>
+  <si>
+    <t>酿酒师</t>
+  </si>
+  <si>
+    <t>酿造啤酒、葡萄酒等。</t>
+  </si>
+  <si>
+    <t>珠宝匠</t>
+  </si>
+  <si>
+    <t>制作金银首饰、奢侈品等。</t>
+  </si>
+  <si>
+    <t>商人</t>
+  </si>
+  <si>
+    <t>运营商店，买卖商品。</t>
+  </si>
+  <si>
+    <t>医生</t>
+  </si>
+  <si>
+    <t>治疗生病的居民。</t>
+  </si>
+  <si>
+    <t>教师</t>
+  </si>
+  <si>
+    <t>在学校中教育儿童。</t>
+  </si>
+  <si>
+    <t>牧师</t>
+  </si>
+  <si>
+    <t>在教堂提供精神服务，维持居民幸福度和稳定度。</t>
+  </si>
+  <si>
+    <t>士兵</t>
+  </si>
+  <si>
+    <t>维持治安，抵御外敌。</t>
+  </si>
+  <si>
+    <t>车夫</t>
+  </si>
+  <si>
+    <t>负责在仓库、生产建筑和市场之间运输货物，提高物流效率。</t>
+  </si>
+  <si>
+    <t>吟游诗人</t>
+  </si>
+  <si>
+    <t>在酒馆表演，提升娱乐度。</t>
+  </si>
+  <si>
+    <t>演员</t>
+  </si>
+  <si>
+    <t>在剧院表演。</t>
+  </si>
+  <si>
+    <t>税务官</t>
+  </si>
+  <si>
+    <t>高效的收取税金，但可能降低居民幸福度。</t>
+  </si>
+  <si>
+    <t>学者</t>
+  </si>
+  <si>
+    <t>在大学中进行研究，解锁新技术，新建筑。</t>
+  </si>
+  <si>
+    <t>贵族</t>
+  </si>
+  <si>
+    <t>消耗大量奢侈品，提供高额税收，但对生活环境要求极高。</t>
+  </si>
+  <si>
+    <t>工程师</t>
+  </si>
+  <si>
+    <t>操作和维护复杂的机械。</t>
+  </si>
+  <si>
+    <t>冒险者</t>
+  </si>
+  <si>
+    <t>探索外部区域，带回稀有资源、宝物或触发特殊事件，但可能有伤亡风险。</t>
+  </si>
+  <si>
+    <t>小偷</t>
+  </si>
+  <si>
+    <t>偷盗居民财产。</t>
   </si>
 </sst>
 </file>
@@ -728,7 +881,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -742,6 +895,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -750,6 +906,13 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1074,9 +1237,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
-    <col min="2" max="3" width="15.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.875" style="4" customWidth="1"/>
     <col min="4" max="4" width="20.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="22.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="80.875" style="2" customWidth="1"/>
     <col min="6" max="7" width="31.125" style="2" customWidth="1"/>
     <col min="8" max="8" width="25.125" style="2" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
@@ -1089,7 +1253,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1112,7 +1276,7 @@
       <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -1135,7 +1299,7 @@
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1151,252 +1315,487 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="2:8">
+    <row r="4" s="2" customFormat="1" spans="2:7">
       <c r="B4" s="4">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="4"/>
+      <c r="E4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="2" t="s">
-        <v>20</v>
+      <c r="G4" s="6">
+        <v>1000</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="2:7">
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" s="2" customFormat="1" spans="2:7">
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" s="2" customFormat="1" spans="2:7">
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="2:7">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" s="3" customFormat="1" spans="1:7">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
     </row>
     <row r="9" s="2" customFormat="1" spans="2:7">
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="B9" s="4">
+        <v>1027</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="4" t="str">
+        <f>_xlfn.CONCAT(C9,"_1")</f>
+        <v>农民_1</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
     </row>
     <row r="10" s="2" customFormat="1" spans="2:7">
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="B10" s="4">
+        <v>1028</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="4" t="str">
+        <f>_xlfn.CONCAT(C10,"_1")</f>
+        <v>樵夫_1</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
     </row>
     <row r="11" s="2" customFormat="1" spans="2:7">
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="B11" s="4">
+        <v>1029</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="4" t="str">
+        <f t="shared" ref="D11:D35" si="0">_xlfn.CONCAT(C11,"_1")</f>
+        <v>渔夫_1</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
     </row>
     <row r="12" s="2" customFormat="1" spans="2:7">
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="B12" s="4">
+        <v>1030</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>矿工_1</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
     </row>
     <row r="13" s="2" customFormat="1" spans="2:7">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="2:6">
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="B13" s="4">
+        <v>1031</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>面包师_1</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="2:7">
+      <c r="B14" s="4">
+        <v>1032</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>厨师_1</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
     </row>
     <row r="15" s="2" customFormat="1" spans="2:7">
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="B15" s="4">
+        <v>1033</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>铁匠_1</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
     </row>
     <row r="16" s="2" customFormat="1" spans="2:7">
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="2:7">
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="2:7">
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-    </row>
-    <row r="19" s="3" customFormat="1" spans="1:7">
-      <c r="A19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="2:8">
+      <c r="B16" s="4">
+        <v>1034</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>木匠_1</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="4">
+        <v>1035</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>裁缝_1</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="4">
+        <v>1036</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>陶工_1</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="4">
+        <v>1037</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>酿酒师_1</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+    </row>
+    <row r="20" spans="2:7">
       <c r="B20" s="4">
-        <v>1002</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="2:7">
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-    </row>
-    <row r="22" s="2" customFormat="1" spans="2:7">
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" s="2" customFormat="1" spans="2:7">
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-    </row>
-    <row r="24" s="2" customFormat="1" spans="2:7">
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="2:7">
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" s="2" customFormat="1" spans="2:7">
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="2:7">
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-    </row>
-    <row r="28" s="2" customFormat="1" spans="2:7">
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-    </row>
-    <row r="29" spans="6:7">
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-    </row>
-    <row r="30" spans="6:6">
-      <c r="F30" s="5"/>
-    </row>
-    <row r="31" spans="6:7">
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-    </row>
-    <row r="32" spans="6:7">
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-    </row>
-    <row r="33" spans="6:7">
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-    </row>
-    <row r="34" spans="6:7">
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
+        <v>1038</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>珠宝匠_1</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="4">
+        <v>1039</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>商人_1</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="4">
+        <v>1040</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>医生_1</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="B23" s="4">
+        <v>1041</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>教师_1</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="B24" s="4">
+        <v>1042</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>牧师_1</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" s="4">
+        <v>1043</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>士兵_1</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="B26" s="4">
+        <v>1044</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>车夫_1</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" s="4">
+        <v>1045</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>吟游诗人_1</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="B28" s="4">
+        <v>1046</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>演员_1</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5">
+      <c r="B29" s="4">
+        <v>1047</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="4" t="str">
+        <f>_xlfn.CONCAT(C29,"_1")</f>
+        <v>税务官_1</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5">
+      <c r="B30" s="4">
+        <v>1048</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" s="4" t="str">
+        <f>_xlfn.CONCAT(C30,"_1")</f>
+        <v>学者_1</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5">
+      <c r="B31" s="4">
+        <v>1049</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D31" s="4" t="str">
+        <f>_xlfn.CONCAT(C31,"_1")</f>
+        <v>贵族_1</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5">
+      <c r="B32" s="4">
+        <v>1050</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="4" t="str">
+        <f>_xlfn.CONCAT(C32,"_1")</f>
+        <v>工程师_1</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5">
+      <c r="B33" s="4">
+        <v>1051</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="4" t="str">
+        <f>_xlfn.CONCAT(C33,"_1")</f>
+        <v>冒险者_1</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5">
+      <c r="B34" s="4">
+        <v>1052</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="4" t="str">
+        <f>_xlfn.CONCAT(C34,"_1")</f>
+        <v>小偷_1</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Packages/cn.etetet.twsunit/Luban/Config/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.twsunit/Luban/Config/Datas/Unit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="21600"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="101">
   <si>
     <t>##var</t>
   </si>
@@ -86,6 +86,9 @@
     <t>金钱_0</t>
   </si>
   <si>
+    <t>Role_027</t>
+  </si>
+  <si>
     <t>钻石_0</t>
   </si>
   <si>
@@ -101,154 +104,232 @@
     <t>种植小麦、蔬菜、水果等农作物。</t>
   </si>
   <si>
+    <t>Role_028</t>
+  </si>
+  <si>
     <t>樵夫</t>
   </si>
   <si>
     <t>砍伐数目，获取木材。</t>
   </si>
   <si>
+    <t>Role_029</t>
+  </si>
+  <si>
     <t>渔夫</t>
   </si>
   <si>
     <t>从河流或海洋中捞捕鱼类。</t>
   </si>
   <si>
+    <t>Role_030</t>
+  </si>
+  <si>
     <t>矿工</t>
   </si>
   <si>
     <t>开采石料、铁、铜、金、煤等矿产资源。</t>
   </si>
   <si>
+    <t>Role_031</t>
+  </si>
+  <si>
     <t>面包师</t>
   </si>
   <si>
     <t>将小麦磨成面粉，再烤制成面包等。</t>
   </si>
   <si>
+    <t>Role_032</t>
+  </si>
+  <si>
     <t>厨师</t>
   </si>
   <si>
     <t>将各种食材加工成高级菜肴。</t>
   </si>
   <si>
+    <t>Role_033</t>
+  </si>
+  <si>
     <t>铁匠</t>
   </si>
   <si>
     <t>将铁锭加工成工具、武器、钉子等。</t>
   </si>
   <si>
+    <t>Role_034</t>
+  </si>
+  <si>
     <t>木匠</t>
   </si>
   <si>
     <t>将木材加工成家具、建材、工具柄等。</t>
   </si>
   <si>
+    <t>Role_035</t>
+  </si>
+  <si>
     <t>裁缝</t>
   </si>
   <si>
     <t>将羊毛、棉花、皮革加工成衣物、皮革制品。</t>
   </si>
   <si>
+    <t>Role_036</t>
+  </si>
+  <si>
     <t>陶工</t>
   </si>
   <si>
     <t>制作陶器、砖块等。</t>
   </si>
   <si>
+    <t>Role_037</t>
+  </si>
+  <si>
     <t>酿酒师</t>
   </si>
   <si>
     <t>酿造啤酒、葡萄酒等。</t>
   </si>
   <si>
+    <t>Role_038</t>
+  </si>
+  <si>
     <t>珠宝匠</t>
   </si>
   <si>
     <t>制作金银首饰、奢侈品等。</t>
   </si>
   <si>
+    <t>Role_039</t>
+  </si>
+  <si>
     <t>商人</t>
   </si>
   <si>
     <t>运营商店，买卖商品。</t>
   </si>
   <si>
+    <t>Role_040</t>
+  </si>
+  <si>
     <t>医生</t>
   </si>
   <si>
     <t>治疗生病的居民。</t>
   </si>
   <si>
+    <t>Role_041</t>
+  </si>
+  <si>
     <t>教师</t>
   </si>
   <si>
     <t>在学校中教育儿童。</t>
   </si>
   <si>
+    <t>Role_042</t>
+  </si>
+  <si>
     <t>牧师</t>
   </si>
   <si>
     <t>在教堂提供精神服务，维持居民幸福度和稳定度。</t>
   </si>
   <si>
+    <t>Role_043</t>
+  </si>
+  <si>
     <t>士兵</t>
   </si>
   <si>
     <t>维持治安，抵御外敌。</t>
   </si>
   <si>
+    <t>Role_044</t>
+  </si>
+  <si>
     <t>车夫</t>
   </si>
   <si>
     <t>负责在仓库、生产建筑和市场之间运输货物，提高物流效率。</t>
   </si>
   <si>
+    <t>Role_045</t>
+  </si>
+  <si>
     <t>吟游诗人</t>
   </si>
   <si>
     <t>在酒馆表演，提升娱乐度。</t>
   </si>
   <si>
+    <t>Role_046</t>
+  </si>
+  <si>
     <t>演员</t>
   </si>
   <si>
     <t>在剧院表演。</t>
   </si>
   <si>
+    <t>Role_047</t>
+  </si>
+  <si>
     <t>税务官</t>
   </si>
   <si>
     <t>高效的收取税金，但可能降低居民幸福度。</t>
   </si>
   <si>
+    <t>Role_048</t>
+  </si>
+  <si>
     <t>学者</t>
   </si>
   <si>
     <t>在大学中进行研究，解锁新技术，新建筑。</t>
   </si>
   <si>
+    <t>Role_049</t>
+  </si>
+  <si>
     <t>贵族</t>
   </si>
   <si>
     <t>消耗大量奢侈品，提供高额税收，但对生活环境要求极高。</t>
   </si>
   <si>
+    <t>Role_050</t>
+  </si>
+  <si>
     <t>工程师</t>
   </si>
   <si>
     <t>操作和维护复杂的机械。</t>
   </si>
   <si>
+    <t>Role_051</t>
+  </si>
+  <si>
     <t>冒险者</t>
   </si>
   <si>
     <t>探索外部区域，带回稀有资源、宝物或触发特殊事件，但可能有伤亡风险。</t>
   </si>
   <si>
+    <t>Role_052</t>
+  </si>
+  <si>
     <t>小偷</t>
   </si>
   <si>
     <t>偷盗居民财产。</t>
+  </si>
+  <si>
+    <t>Role_053</t>
   </si>
 </sst>
 </file>
@@ -1315,7 +1396,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="2:7">
+    <row r="4" s="2" customFormat="1" spans="2:8">
       <c r="B4" s="4">
         <v>1</v>
       </c>
@@ -1331,6 +1412,9 @@
       </c>
       <c r="G4" s="6">
         <v>1000</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="2:7">
@@ -1339,7 +1423,7 @@
       <c r="D5" s="4"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" s="6">
         <v>0</v>
@@ -1351,7 +1435,7 @@
       <c r="D6" s="4"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G6" s="6">
         <v>0</v>
@@ -1363,7 +1447,7 @@
       <c r="D7" s="4"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" s="6">
         <v>2</v>
@@ -1380,421 +1464,499 @@
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" s="2" customFormat="1" spans="2:7">
+    <row r="9" s="2" customFormat="1" spans="2:8">
       <c r="B9" s="4">
         <v>1027</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" s="4" t="str">
         <f>_xlfn.CONCAT(C9,"_1")</f>
         <v>农民_1</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="2:7">
+      <c r="H9" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" spans="2:8">
       <c r="B10" s="4">
         <v>1028</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D10" s="4" t="str">
         <f>_xlfn.CONCAT(C10,"_1")</f>
         <v>樵夫_1</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="2:7">
+      <c r="H10" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" spans="2:8">
       <c r="B11" s="4">
         <v>1029</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D11" s="4" t="str">
         <f t="shared" ref="D11:D35" si="0">_xlfn.CONCAT(C11,"_1")</f>
         <v>渔夫_1</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="2:7">
+      <c r="H11" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="2:8">
       <c r="B12" s="4">
         <v>1030</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D12" s="4" t="str">
         <f t="shared" si="0"/>
         <v>矿工_1</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="2:7">
+      <c r="H12" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" spans="2:8">
       <c r="B13" s="4">
         <v>1031</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>面包师_1</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="2:7">
+      <c r="H13" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="2:8">
       <c r="B14" s="4">
         <v>1032</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>厨师_1</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="2:7">
+      <c r="H14" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="2:8">
       <c r="B15" s="4">
         <v>1033</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D15" s="4" t="str">
         <f t="shared" si="0"/>
         <v>铁匠_1</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="2:7">
+      <c r="H15" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="2:8">
       <c r="B16" s="4">
         <v>1034</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D16" s="4" t="str">
         <f t="shared" si="0"/>
         <v>木匠_1</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="2:7">
+      <c r="H16" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
       <c r="B17" s="4">
         <v>1035</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D17" s="4" t="str">
         <f t="shared" si="0"/>
         <v>裁缝_1</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
-    </row>
-    <row r="18" spans="2:6">
+      <c r="H17" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
       <c r="B18" s="4">
         <v>1036</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>陶工_1</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F18" s="6"/>
-    </row>
-    <row r="19" spans="2:7">
+      <c r="H18" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8">
       <c r="B19" s="4">
         <v>1037</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D19" s="4" t="str">
         <f t="shared" si="0"/>
         <v>酿酒师_1</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
-    </row>
-    <row r="20" spans="2:7">
+      <c r="H19" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8">
       <c r="B20" s="4">
         <v>1038</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D20" s="4" t="str">
         <f t="shared" si="0"/>
         <v>珠宝匠_1</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
-    </row>
-    <row r="21" spans="2:7">
+      <c r="H20" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8">
       <c r="B21" s="4">
         <v>1039</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D21" s="10" t="str">
         <f t="shared" si="0"/>
         <v>商人_1</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
-    </row>
-    <row r="22" spans="2:7">
+      <c r="H21" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8">
       <c r="B22" s="4">
         <v>1040</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D22" s="4" t="str">
         <f t="shared" si="0"/>
         <v>医生_1</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
-    </row>
-    <row r="23" spans="2:5">
+      <c r="H22" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8">
       <c r="B23" s="4">
         <v>1041</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D23" s="4" t="str">
         <f t="shared" si="0"/>
         <v>教师_1</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5">
+        <v>66</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8">
       <c r="B24" s="4">
         <v>1042</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D24" s="4" t="str">
         <f t="shared" si="0"/>
         <v>牧师_1</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5">
+        <v>69</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8">
       <c r="B25" s="4">
         <v>1043</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="D25" s="4" t="str">
         <f t="shared" si="0"/>
         <v>士兵_1</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5">
+        <v>72</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8">
       <c r="B26" s="4">
         <v>1044</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="D26" s="4" t="str">
         <f t="shared" si="0"/>
         <v>车夫_1</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5">
+        <v>75</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8">
       <c r="B27" s="4">
         <v>1045</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D27" s="4" t="str">
         <f t="shared" si="0"/>
         <v>吟游诗人_1</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5">
+        <v>78</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8">
       <c r="B28" s="4">
         <v>1046</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D28" s="4" t="str">
         <f t="shared" si="0"/>
         <v>演员_1</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5">
+        <v>81</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8">
       <c r="B29" s="4">
         <v>1047</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="D29" s="4" t="str">
-        <f>_xlfn.CONCAT(C29,"_1")</f>
+        <f t="shared" si="0"/>
         <v>税务官_1</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5">
+        <v>84</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8">
       <c r="B30" s="4">
         <v>1048</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D30" s="4" t="str">
-        <f>_xlfn.CONCAT(C30,"_1")</f>
+        <f t="shared" si="0"/>
         <v>学者_1</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5">
+        <v>87</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8">
       <c r="B31" s="4">
         <v>1049</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="D31" s="4" t="str">
-        <f>_xlfn.CONCAT(C31,"_1")</f>
+        <f t="shared" si="0"/>
         <v>贵族_1</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5">
+        <v>90</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8">
       <c r="B32" s="4">
         <v>1050</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="D32" s="4" t="str">
-        <f>_xlfn.CONCAT(C32,"_1")</f>
+        <f t="shared" si="0"/>
         <v>工程师_1</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5">
+        <v>93</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8">
       <c r="B33" s="4">
         <v>1051</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="D33" s="4" t="str">
-        <f>_xlfn.CONCAT(C33,"_1")</f>
+        <f t="shared" si="0"/>
         <v>冒险者_1</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5">
+        <v>96</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8">
       <c r="B34" s="4">
         <v>1052</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="D34" s="4" t="str">
-        <f>_xlfn.CONCAT(C34,"_1")</f>
+        <f t="shared" si="0"/>
         <v>小偷_1</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>73</v>
+        <v>99</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.twsunit/Luban/Config/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.twsunit/Luban/Config/Datas/Unit.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600"/>
+    <workbookView windowWidth="21600" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
+    <sheet name="Player" sheetId="2" r:id="rId1"/>
+    <sheet name="UnitProto" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="102">
   <si>
     <t>##var</t>
   </si>
@@ -78,6 +79,9 @@
   </si>
   <si>
     <t>资源名称</t>
+  </si>
+  <si>
+    <t>玩家</t>
   </si>
   <si>
     <t>管理者</t>
@@ -1314,6 +1318,140 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" outlineLevelRow="6" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="20.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="80.875" style="2" customWidth="1"/>
+    <col min="6" max="7" width="31.125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="25.125" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="2:7">
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" s="2" customFormat="1" spans="2:7">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="2:7">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="2:7">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" outlineLevelCol="7"/>
   <cols>
@@ -1398,23 +1536,23 @@
     </row>
     <row r="4" s="2" customFormat="1" spans="2:8">
       <c r="B4" s="4">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4" s="6">
         <v>1000</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="2:7">
@@ -1423,7 +1561,7 @@
       <c r="D5" s="4"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5" s="6">
         <v>0</v>
@@ -1435,7 +1573,7 @@
       <c r="D6" s="4"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="6">
         <v>0</v>
@@ -1447,7 +1585,7 @@
       <c r="D7" s="4"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" s="6">
         <v>2</v>
@@ -1466,497 +1604,497 @@
     </row>
     <row r="9" s="2" customFormat="1" spans="2:8">
       <c r="B9" s="4">
-        <v>1027</v>
+        <v>1002</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" s="4" t="str">
         <f>_xlfn.CONCAT(C9,"_1")</f>
         <v>农民_1</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" spans="2:8">
       <c r="B10" s="4">
-        <v>1028</v>
+        <v>1003</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" s="4" t="str">
         <f>_xlfn.CONCAT(C10,"_1")</f>
         <v>樵夫_1</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" spans="2:8">
       <c r="B11" s="4">
-        <v>1029</v>
+        <v>1004</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" s="4" t="str">
         <f t="shared" ref="D11:D35" si="0">_xlfn.CONCAT(C11,"_1")</f>
         <v>渔夫_1</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="2:8">
       <c r="B12" s="4">
-        <v>1030</v>
+        <v>1005</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" s="4" t="str">
         <f t="shared" si="0"/>
         <v>矿工_1</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" spans="2:8">
       <c r="B13" s="4">
-        <v>1031</v>
+        <v>1006</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>面包师_1</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" spans="2:8">
       <c r="B14" s="4">
-        <v>1032</v>
+        <v>1007</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>厨师_1</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" spans="2:8">
       <c r="B15" s="4">
-        <v>1033</v>
+        <v>1008</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="4" t="str">
         <f t="shared" si="0"/>
         <v>铁匠_1</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" spans="2:8">
       <c r="B16" s="4">
-        <v>1034</v>
+        <v>1009</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="4" t="str">
         <f t="shared" si="0"/>
         <v>木匠_1</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="2:8">
       <c r="B17" s="4">
-        <v>1035</v>
+        <v>1010</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D17" s="4" t="str">
         <f t="shared" si="0"/>
         <v>裁缝_1</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" s="4">
-        <v>1036</v>
+        <v>1011</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>陶工_1</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" s="6"/>
       <c r="H18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" s="4">
-        <v>1037</v>
+        <v>1012</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D19" s="4" t="str">
         <f t="shared" si="0"/>
         <v>酿酒师_1</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="2:8">
       <c r="B20" s="4">
-        <v>1038</v>
+        <v>1013</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D20" s="4" t="str">
         <f t="shared" si="0"/>
         <v>珠宝匠_1</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="2:8">
       <c r="B21" s="4">
-        <v>1039</v>
+        <v>1014</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D21" s="10" t="str">
         <f t="shared" si="0"/>
         <v>商人_1</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="2:8">
       <c r="B22" s="4">
-        <v>1040</v>
+        <v>1015</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D22" s="4" t="str">
         <f t="shared" si="0"/>
         <v>医生_1</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="2:8">
       <c r="B23" s="4">
-        <v>1041</v>
+        <v>1016</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D23" s="4" t="str">
         <f t="shared" si="0"/>
         <v>教师_1</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="2:8">
       <c r="B24" s="4">
-        <v>1042</v>
+        <v>1017</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D24" s="4" t="str">
         <f t="shared" si="0"/>
         <v>牧师_1</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="2:8">
       <c r="B25" s="4">
-        <v>1043</v>
+        <v>1018</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D25" s="4" t="str">
         <f t="shared" si="0"/>
         <v>士兵_1</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="2:8">
       <c r="B26" s="4">
-        <v>1044</v>
+        <v>1019</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26" s="4" t="str">
         <f t="shared" si="0"/>
         <v>车夫_1</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="2:8">
       <c r="B27" s="4">
-        <v>1045</v>
+        <v>1020</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" s="4" t="str">
         <f t="shared" si="0"/>
         <v>吟游诗人_1</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="2:8">
       <c r="B28" s="4">
-        <v>1046</v>
+        <v>1021</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D28" s="4" t="str">
         <f t="shared" si="0"/>
         <v>演员_1</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="2:8">
       <c r="B29" s="4">
-        <v>1047</v>
+        <v>1022</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D29" s="4" t="str">
         <f t="shared" si="0"/>
         <v>税务官_1</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="2:8">
       <c r="B30" s="4">
-        <v>1048</v>
+        <v>1023</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D30" s="4" t="str">
         <f t="shared" si="0"/>
         <v>学者_1</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="2:8">
       <c r="B31" s="4">
-        <v>1049</v>
+        <v>1024</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D31" s="4" t="str">
         <f t="shared" si="0"/>
         <v>贵族_1</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="2:8">
       <c r="B32" s="4">
-        <v>1050</v>
+        <v>1025</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D32" s="4" t="str">
         <f t="shared" si="0"/>
         <v>工程师_1</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" s="4">
-        <v>1051</v>
+        <v>1026</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D33" s="4" t="str">
         <f t="shared" si="0"/>
         <v>冒险者_1</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="2:8">
       <c r="B34" s="4">
-        <v>1052</v>
+        <v>1027</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D34" s="4" t="str">
         <f t="shared" si="0"/>
         <v>小偷_1</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
